--- a/output/pdf_financials_xlsx/SOI.xlsx
+++ b/output/pdf_financials_xlsx/SOI.xlsx
@@ -2499,19 +2499,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000892</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.207974</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000711</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.771227</v>
@@ -2523,22 +2523,22 @@
         <v>2.258776</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.346704</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.301569</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.585502</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.107538</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.3756</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.345601</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.913639</v>
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000892</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.207974</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000711</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.771227</v>
@@ -2633,22 +2633,22 @@
         <v>2.258776</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.346704</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.301569</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.585502</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.107538</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.3756</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.345601</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.913639</v>
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.3e-05</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000812</v>
+        <v>0.000783</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000714</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.445822</v>
+        <v>1.237848</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3293,22 +3293,22 @@
         <v>3.303903</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.409333</v>
+        <v>3.062629</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.468951</v>
+        <v>2.167382</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.953194</v>
+        <v>1.367692</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.013129</v>
+        <v>0.905591</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.310347</v>
+        <v>0.934747</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.490838</v>
+        <v>1.145237</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.344442</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">

--- a/output/pdf_financials_xlsx/SOI.xlsx
+++ b/output/pdf_financials_xlsx/SOI.xlsx
@@ -2175,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.017981</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.022921</v>
       </c>
     </row>
     <row r="29">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.000921</v>
+        <v>-0.98294</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.163619</v>
+        <v>-1.140698</v>
       </c>
     </row>
     <row r="30">
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.017981</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.022921</v>
       </c>
     </row>
     <row r="101">
@@ -21460,7 +21460,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -38704,7 +38708,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SOI.xlsx
+++ b/output/pdf_financials_xlsx/SOI.xlsx
@@ -795,49 +795,49 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.00133</v>
+        <v>0.001716</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.00146</v>
+        <v>0.001949</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.008919</v>
+        <v>0.016052</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.000568</v>
+        <v>0.000987</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.034271</v>
+        <v>0.043708</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.237084</v>
+        <v>0.251623</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.092571</v>
+        <v>0.115742</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.111297</v>
+        <v>0.133598</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.020435</v>
+        <v>0.045084</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.00193</v>
+        <v>0.021946</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.002514</v>
+        <v>0.031798</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.001596</v>
+        <v>0.027379</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.002704</v>
+        <v>0.023171</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.003204</v>
+        <v>0.042914</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.010539</v>
+        <v>0.038835</v>
       </c>
     </row>
     <row r="8">
@@ -4553,10 +4553,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.020698</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.022362</v>
       </c>
     </row>
     <row r="71">
@@ -4608,10 +4608,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.020698</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.022362</v>
       </c>
     </row>
     <row r="72">
@@ -4828,10 +4828,10 @@
         <v>1.299416</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.345825</v>
+        <v>0.325127</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.443164</v>
+        <v>1.420802</v>
       </c>
     </row>
     <row r="76">
@@ -5138,15 +5138,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P80" s="3" t="n">
+        <v>0.0005742624439852738</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.0006059499340979994</v>
       </c>
     </row>
     <row r="81">
@@ -9600,7 +9596,11 @@
           <t>Current portion of lease obligation</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -38556,7 +38556,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -47830,7 +47834,11 @@
           <t>Office expenses 9 437</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -52862,7 +52870,11 @@
           <t>Office expenses 7 133</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -55814,7 +55826,11 @@
           <t>Office expenses 6 489</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
